--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU13"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46188.85416666666</v>
+        <v>46188.83333333334</v>
       </c>
     </row>
     <row r="11">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46188.875</v>
+        <v>46188.85416666666</v>
       </c>
     </row>
     <row r="13">
@@ -2442,141 +2442,300 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" s="3" t="n">
+        <v>46188.875</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>Criciúma</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Ceará</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" s="3" t="n">
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3" t="n">
         <v>46188.875</v>
       </c>
     </row>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N10" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1529,55 +1529,55 @@
         <v>3.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,40 +1688,40 @@
         <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC8" t="n">
         <v>1.91</v>
@@ -1730,13 +1730,13 @@
         <v>1.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,55 +1847,55 @@
         <v>4.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,55 +2006,55 @@
         <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="O9" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="P9" t="n">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.27</v>
+        <v>2.13</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.92</v>
+        <v>2.53</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.08</v>
+        <v>3.9</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.98</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.72</v>
       </c>
-      <c r="AC9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AG9" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.97</v>
+        <v>2.13</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>5.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
         <v>1.3</v>
@@ -2051,10 +2051,10 @@
         <v>1.52</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1361,25 +1361,25 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
         <v>3.55</v>
       </c>
       <c r="R6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S6" t="n">
         <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="U6" t="n">
         <v>2.6</v>
@@ -1388,7 +1388,7 @@
         <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
@@ -1397,25 +1397,25 @@
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.19</v>
+        <v>3.84</v>
       </c>
       <c r="AA6" t="n">
         <v>1.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
         <v>2.85</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
         <v>2.25</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,58 +1520,58 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.28</v>
+        <v>2.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="AA7" t="n">
         <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
         <v>1.57</v>
@@ -1593,7 +1593,7 @@
         <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,34 +1679,34 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>3.39</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
         <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
@@ -1718,16 +1718,16 @@
         <v>5.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB8" t="n">
         <v>2.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
         <v>1.33</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AK8" t="n">
         <v>1.36</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1871,7 +1871,7 @@
         <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
         <v>3.9</v>
@@ -1883,10 +1883,10 @@
         <v>1.98</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE9" t="n">
         <v>1.1</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46188.77083333334</v>
+        <v>46188.8125</v>
       </c>
     </row>
     <row r="10">
@@ -2171,49 +2171,49 @@
         <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.92</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
         <v>1.67</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
         <v>3.4</v>
@@ -1370,16 +1370,16 @@
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R6" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="S6" t="n">
         <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
         <v>2.6</v>
@@ -1391,16 +1391,16 @@
         <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AB6" t="n">
         <v>2.05</v>
@@ -1415,10 +1415,10 @@
         <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.7</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="O7" t="n">
         <v>3.35</v>
@@ -1529,13 +1529,13 @@
         <v>2.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
         <v>3.25</v>
@@ -1547,25 +1547,25 @@
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AA7" t="n">
         <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="AD7" t="n">
         <v>1.38</v>
@@ -1593,7 +1593,7 @@
         <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1685,13 +1685,13 @@
         <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.39</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
@@ -1700,28 +1700,28 @@
         <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="V8" t="n">
         <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.75</v>
+        <v>5.87</v>
       </c>
       <c r="AA8" t="n">
         <v>1.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="AC8" t="n">
         <v>1.97</v>
@@ -1730,7 +1730,7 @@
         <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF8" t="n">
         <v>1.35</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
         <v>1.36</v>
@@ -1856,46 +1856,46 @@
         <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="U9" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z9" t="n">
         <v>3.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE9" t="n">
         <v>1.1</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>1.54</v>
       </c>
       <c r="R10" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="S10" t="n">
         <v>1.13</v>
@@ -2018,7 +2018,7 @@
         <v>5.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
         <v>1.94</v>
@@ -2039,7 +2039,7 @@
         <v>1.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
         <v>1.6</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.85</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.83</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1364,7 +1364,7 @@
         <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P6" t="n">
         <v>1.94</v>
@@ -1379,7 +1379,7 @@
         <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="U6" t="n">
         <v>2.6</v>
@@ -1388,16 +1388,16 @@
         <v>1.45</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
         <v>1.73</v>
@@ -1406,7 +1406,7 @@
         <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="AD6" t="n">
         <v>1.37</v>
@@ -1415,10 +1415,10 @@
         <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AK6" t="n">
         <v>1.28</v>
@@ -1529,7 +1529,7 @@
         <v>2.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>2.18</v>
@@ -1538,7 +1538,7 @@
         <v>1.32</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="U7" t="n">
         <v>2.4</v>
@@ -1593,7 +1593,7 @@
         <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,10 +1688,10 @@
         <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
@@ -1700,13 +1700,13 @@
         <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
         <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
@@ -1718,7 +1718,7 @@
         <v>5.87</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB8" t="n">
         <v>2.77</v>
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="Q9" t="n">
         <v>2.13</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.06</v>
+        <v>2.92</v>
       </c>
       <c r="U9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -1871,31 +1871,31 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.9</v>
+        <v>3.94</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>5.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="W10" t="n">
         <v>1.3</v>
@@ -2036,7 +2036,7 @@
         <v>7.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
@@ -2054,7 +2054,7 @@
         <v>1.59</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
         <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>1.44</v>
@@ -2177,7 +2177,7 @@
         <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
         <v>1.31</v>
@@ -2198,7 +2198,7 @@
         <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
         <v>3.58</v>
@@ -2210,7 +2210,7 @@
         <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
         <v>1.85</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
         <v>1.67</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2159,61 +2159,61 @@
         <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2318,61 +2318,61 @@
         <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2159,61 +2159,61 @@
         <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2318,61 +2318,61 @@
         <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
         <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="Q9" t="n">
         <v>2.13</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="T9" t="n">
-        <v>2.92</v>
+        <v>2.97</v>
       </c>
       <c r="U9" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -1871,31 +1871,31 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AC9" t="n">
         <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
         <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="R10" t="n">
         <v>2.98</v>
@@ -2015,7 +2015,7 @@
         <v>1.13</v>
       </c>
       <c r="T10" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="U10" t="n">
         <v>1.67</v>
@@ -2033,10 +2033,10 @@
         <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
@@ -2048,7 +2048,7 @@
         <v>2.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AF10" t="n">
         <v>1.59</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.67</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2318,61 +2318,61 @@
         <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1370,25 +1370,25 @@
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
         <v>2.36</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="U6" t="n">
         <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1</v>
@@ -1397,7 +1397,7 @@
         <v>1.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>4</v>
+        <v>4.16</v>
       </c>
       <c r="AA6" t="n">
         <v>1.73</v>
@@ -1415,7 +1415,7 @@
         <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
         <v>2.2</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,28 +1520,28 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="R7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
@@ -1553,25 +1553,25 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="AA7" t="n">
         <v>1.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AD7" t="n">
         <v>1.38</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF7" t="n">
         <v>1.57</v>
@@ -1593,7 +1593,7 @@
         <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,16 +1679,16 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="R8" t="n">
         <v>2.5</v>
@@ -1700,28 +1700,28 @@
         <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="V8" t="n">
         <v>1.73</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
         <v>5.87</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
         <v>1.97</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1838,31 +1838,31 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>2.13</v>
       </c>
       <c r="R9" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="U9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
@@ -1874,22 +1874,22 @@
         <v>1.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC9" t="n">
         <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF9" t="n">
         <v>1.78</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AK9" t="n">
         <v>2.2</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
         <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>3.67</v>
+        <v>3.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2348,10 +2348,10 @@
         <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="AA12" t="n">
         <v>2.08</v>
@@ -2369,7 +2369,7 @@
         <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
         <v>1.85</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
         <v>1.67</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2006,7 +2006,7 @@
         <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="R10" t="n">
         <v>2.98</v>
@@ -2036,25 +2036,25 @@
         <v>7.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AB10" t="n">
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AF10" t="n">
         <v>1.59</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2024,7 +2024,7 @@
         <v>2.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -2039,16 +2039,16 @@
         <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AF10" t="n">
         <v>1.59</v>
@@ -2070,7 +2070,7 @@
         <v>1.06</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2159,61 +2159,61 @@
         <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2318,61 +2318,61 @@
         <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="O2" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1370,49 +1370,49 @@
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>4.13</v>
       </c>
       <c r="R6" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="U6" t="n">
         <v>2.6</v>
       </c>
       <c r="V6" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
         <v>4.16</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
         <v>1.6</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="AK6" t="n">
         <v>1.27</v>
@@ -1523,25 +1523,25 @@
         <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T7" t="n">
         <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
@@ -1550,31 +1550,31 @@
         <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.82</v>
+        <v>4.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB7" t="n">
         <v>2.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG7" t="n">
         <v>2.2</v>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
         <v>1.75</v>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.78</v>
+        <v>2.93</v>
       </c>
       <c r="O8" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="P8" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
         <v>2.92</v>
       </c>
       <c r="R8" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
@@ -1700,7 +1700,7 @@
         <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="V8" t="n">
         <v>1.73</v>
@@ -1712,13 +1712,13 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.87</v>
+        <v>5.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB8" t="n">
         <v>2.75</v>
@@ -1841,61 +1841,61 @@
         <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>5.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="R9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
         <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
         <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AC9" t="n">
         <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2018,10 +2018,10 @@
         <v>5.1</v>
       </c>
       <c r="U10" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V10" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="W10" t="n">
         <v>1.32</v>
@@ -2033,19 +2033,19 @@
         <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
         <v>1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AE10" t="n">
         <v>1.52</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>4.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2318,61 +2318,61 @@
         <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="P8" t="n">
         <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
         <v>1.2</v>
@@ -1712,31 +1712,31 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.65</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC8" t="n">
         <v>1.97</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF8" t="n">
         <v>1.35</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.19</v>
+        <v>1.65</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2006,22 +2006,22 @@
         <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="S10" t="n">
         <v>1.13</v>
       </c>
       <c r="T10" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="W10" t="n">
         <v>1.32</v>
@@ -2033,28 +2033,28 @@
         <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>4.06</v>
+        <v>3.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.81</v>
       </c>
       <c r="P12" t="n">
-        <v>3.3</v>
+        <v>4.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="O2" t="n">
         <v>2.75</v>
       </c>
       <c r="P2" t="n">
-        <v>2.87</v>
+        <v>2.98</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -893,55 +893,55 @@
         <v>2.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="P4" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>2.6</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="O6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T6" t="n">
         <v>3.25</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.91</v>
-      </c>
       <c r="U6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
@@ -1394,16 +1394,16 @@
         <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC6" t="n">
         <v>2.75</v>
@@ -1412,10 +1412,10 @@
         <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
         <v>2.2</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,22 +1520,22 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.96</v>
+        <v>2.19</v>
       </c>
       <c r="O7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P7" t="n">
-        <v>2.71</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="S7" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
         <v>3.25</v>
@@ -1547,22 +1547,22 @@
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="AC7" t="n">
         <v>2.45</v>
@@ -1574,7 +1574,7 @@
         <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG7" t="n">
         <v>2.2</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1838,55 +1838,55 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>5.18</v>
+        <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="T9" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="Z9" t="n">
         <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC9" t="n">
         <v>2.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE9" t="n">
         <v>1.13</v>
@@ -1895,7 +1895,7 @@
         <v>1.67</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2162,43 +2162,43 @@
         <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
         <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="S11" t="n">
         <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="V11" t="n">
         <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA11" t="n">
         <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
         <v>3.58</v>
@@ -2207,10 +2207,10 @@
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
         <v>1.85</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
         <v>1.67</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O12" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="P12" t="n">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="P2" t="n">
-        <v>2.98</v>
+        <v>3.41</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.9</v>
+        <v>3.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="V2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
         <v>5.5</v>
@@ -776,13 +776,13 @@
         <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
         <v>1.5</v>
@@ -884,25 +884,25 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.78</v>
+        <v>2.41</v>
       </c>
       <c r="O3" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
-        <v>2.64</v>
+        <v>3.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>3.26</v>
       </c>
       <c r="R3" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="S3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="U3" t="n">
         <v>3.98</v>
@@ -911,16 +911,16 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AA3" t="n">
         <v>2.75</v>
@@ -929,16 +929,16 @@
         <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
         <v>1.01</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AG3" t="n">
         <v>1.54</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1208,7 +1208,7 @@
         <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1367,25 +1367,25 @@
         <v>3.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
@@ -1400,13 +1400,13 @@
         <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
         <v>2.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="AD6" t="n">
         <v>1.43</v>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         <v>1.12</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
         <v>2.2</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="O8" t="n">
         <v>3.6</v>
@@ -1712,10 +1712,10 @@
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.9</v>
+        <v>5.65</v>
       </c>
       <c r="AA8" t="n">
         <v>1.36</v>
@@ -1724,16 +1724,16 @@
         <v>2.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AD8" t="n">
         <v>1.74</v>
       </c>
       <c r="AE8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.35</v>
       </c>
       <c r="AG8" t="n">
         <v>2.9</v>
@@ -1847,7 +1847,7 @@
         <v>4.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="R9" t="n">
         <v>2.25</v>
@@ -1862,7 +1862,7 @@
         <v>2.45</v>
       </c>
       <c r="V9" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W9" t="n">
         <v>1.07</v>
@@ -1889,7 +1889,7 @@
         <v>1.38</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF9" t="n">
         <v>1.67</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="S10" t="n">
         <v>1.13</v>
@@ -2207,13 +2207,13 @@
         <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
         <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>2.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AB12" t="n">
         <v>1.4</v>
@@ -2369,7 +2369,7 @@
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
         <v>1.55</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="O8" t="n">
         <v>3.6</v>
@@ -1697,13 +1697,13 @@
         <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
         <v>1.18</v>
@@ -1841,10 +1841,10 @@
         <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q9" t="n">
         <v>2.15</v>
@@ -1871,7 +1871,7 @@
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
         <v>3.95</v>
@@ -1883,10 +1883,10 @@
         <v>2.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AE9" t="n">
         <v>1.11</v>
@@ -2024,7 +2024,7 @@
         <v>2.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="X10" t="n">
         <v>1</v>
@@ -2036,19 +2036,19 @@
         <v>7.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AF10" t="n">
         <v>1.57</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R11" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AA11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.08</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O12" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>4.08</v>
+        <v>3.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.77</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="U12" t="n">
-        <v>3.74</v>
+        <v>2.97</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.15</v>
+        <v>3.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1841,13 +1841,13 @@
         <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
         <v>2.25</v>
@@ -1856,13 +1856,13 @@
         <v>1.34</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
         <v>1.07</v>
@@ -1874,28 +1874,28 @@
         <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AA9" t="n">
         <v>1.68</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE9" t="n">
         <v>1.11</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2033,13 +2033,13 @@
         <v>1.03</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AC10" t="n">
         <v>1.6</v>
@@ -2165,7 +2165,7 @@
         <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.91</v>
@@ -2174,7 +2174,7 @@
         <v>1.62</v>
       </c>
       <c r="T11" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="U11" t="n">
         <v>3.6</v>
@@ -2192,10 +2192,10 @@
         <v>1.46</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.77</v>
+        <v>2.48</v>
       </c>
       <c r="AB11" t="n">
         <v>1.4</v>
@@ -2207,7 +2207,7 @@
         <v>1.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
         <v>2.08</v>
@@ -2372,7 +2372,7 @@
         <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1841,13 +1841,13 @@
         <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P9" t="n">
-        <v>4.55</v>
+        <v>4.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
         <v>2.25</v>
@@ -1856,7 +1856,7 @@
         <v>1.34</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="U9" t="n">
         <v>2.4</v>
@@ -1868,22 +1868,22 @@
         <v>1.07</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AB9" t="n">
         <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AD9" t="n">
         <v>1.4</v>
@@ -1911,7 +1911,7 @@
         <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>1.21</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
         <v>1.6</v>
@@ -2165,10 +2165,10 @@
         <v>3.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R11" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="S11" t="n">
         <v>1.62</v>
@@ -2198,7 +2198,7 @@
         <v>2.48</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC11" t="n">
         <v>5.15</v>
@@ -2210,10 +2210,10 @@
         <v>1.03</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>2.7</v>
       </c>
       <c r="R12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
         <v>1.44</v>
@@ -2345,7 +2345,7 @@
         <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
         <v>1.4</v>
@@ -2372,7 +2372,7 @@
         <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>3.18</v>
+        <v>3.13</v>
       </c>
       <c r="P13" t="n">
-        <v>3.32</v>
+        <v>3.99</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.99</v>
+        <v>2.19</v>
       </c>
       <c r="O14" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="P14" t="n">
-        <v>3.99</v>
+        <v>3.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>3.41</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.36</v>
+        <v>3.55</v>
       </c>
       <c r="R2" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="T2" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y2" t="n">
         <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.04</v>
+        <v>2.74</v>
       </c>
       <c r="AB2" t="n">
         <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AD2" t="n">
         <v>1.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,43 +884,43 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
         <v>1.78</v>
       </c>
       <c r="S3" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="T3" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>3.98</v>
+        <v>4.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
         <v>1.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AA3" t="n">
         <v>2.75</v>
@@ -929,16 +929,16 @@
         <v>1.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.5</v>
+        <v>6.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AG3" t="n">
         <v>1.54</v>
@@ -957,7 +957,7 @@
         <v>1.33</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1364,16 +1364,16 @@
         <v>3.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S6" t="n">
         <v>1.35</v>
@@ -1382,10 +1382,10 @@
         <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
@@ -1394,28 +1394,28 @@
         <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
         <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG6" t="n">
         <v>2.2</v>
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="O7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>2.71</v>
       </c>
       <c r="Q7" t="n">
         <v>2.4</v>
@@ -1541,7 +1541,7 @@
         <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
@@ -1559,22 +1559,22 @@
         <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
         <v>2.2</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="O8" t="n">
         <v>3.6</v>
@@ -1703,7 +1703,7 @@
         <v>2.09</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W8" t="n">
         <v>1.18</v>
@@ -1715,22 +1715,22 @@
         <v>1.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.65</v>
+        <v>6.23</v>
       </c>
       <c r="AA8" t="n">
         <v>1.36</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AF8" t="n">
         <v>1.33</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
         <v>1.36</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barra do Garcas</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.13</v>
+        <v>2.55</v>
       </c>
       <c r="U11" t="n">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.48</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.15</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Barra do Garcas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P12" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="T12" t="n">
-        <v>2.55</v>
+        <v>2.13</v>
       </c>
       <c r="U12" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.08</v>
+        <v>2.48</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.58</v>
+        <v>5.15</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -702,26 +702,26 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -734,28 +734,28 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
         <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="T2" t="n">
         <v>1.98</v>
       </c>
       <c r="U2" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Y2" t="n">
         <v>1.59</v>
@@ -764,13 +764,13 @@
         <v>2.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AB2" t="n">
         <v>1.44</v>
       </c>
       <c r="AC2" t="n">
-        <v>7</v>
+        <v>5.15</v>
       </c>
       <c r="AD2" t="n">
         <v>1.1</v>
@@ -786,46 +786,46 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '85']</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46188.29166666666</v>
@@ -884,19 +884,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="O3" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="P3" t="n">
         <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="R3" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="S3" t="n">
         <v>1.59</v>
@@ -905,10 +905,10 @@
         <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>4.1</v>
+        <v>3.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
@@ -920,7 +920,7 @@
         <v>1.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AA3" t="n">
         <v>2.75</v>
@@ -932,7 +932,7 @@
         <v>6.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE3" t="n">
         <v>1.03</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.33</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="P5" t="n">
-        <v>3.33</v>
+        <v>2.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1367,28 +1367,28 @@
         <v>3.3</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="R6" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
@@ -1400,22 +1400,22 @@
         <v>4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.77</v>
+        <v>2.68</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG6" t="n">
         <v>2.2</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="O7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
         <v>2.71</v>
@@ -1532,52 +1532,52 @@
         <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
         <v>3.25</v>
       </c>
       <c r="U7" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.33</v>
+        <v>4.56</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF7" t="n">
         <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -861,26 +861,26 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
@@ -945,7 +945,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37', '90+5']</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -963,28 +963,28 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46188.375</v>
@@ -1020,26 +1020,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['41', '53']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
@@ -1122,28 +1122,28 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46188.41666666666</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1182,13 +1182,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
@@ -1281,28 +1281,28 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46188.5</v>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>3.3</v>
@@ -1373,52 +1373,52 @@
         <v>3.78</v>
       </c>
       <c r="R6" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="S6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T6" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.49</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.47</v>
-      </c>
       <c r="AE6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF6" t="n">
         <v>1.57</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
         <v>1.33</v>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="R7" t="n">
         <v>2.3</v>
@@ -1538,46 +1538,46 @@
         <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U7" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V7" t="n">
         <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
         <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.66</v>
+        <v>2.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,58 +1679,58 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>2.38</v>
       </c>
       <c r="O8" t="n">
         <v>3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T8" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.09</v>
+        <v>1.93</v>
       </c>
       <c r="V8" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X8" t="n">
         <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.23</v>
+        <v>6.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB8" t="n">
         <v>2.88</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AD8" t="n">
         <v>1.8</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AF8" t="n">
         <v>1.33</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK8" t="n">
         <v>1.36</v>
@@ -1841,46 +1841,46 @@
         <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P9" t="n">
         <v>4.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T9" t="n">
         <v>3.1</v>
       </c>
       <c r="U9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V9" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC9" t="n">
         <v>3.05</v>
@@ -1889,7 +1889,7 @@
         <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
         <v>1.7</v>
@@ -1908,7 +1908,7 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK9" t="n">
         <v>2.08</v>
@@ -2009,7 +2009,7 @@
         <v>1.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="S10" t="n">
         <v>1.13</v>
@@ -2030,10 +2030,10 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AA10" t="n">
         <v>1.21</v>
@@ -2042,13 +2042,13 @@
         <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
         <v>1.57</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="O11" t="n">
         <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
         <v>2.7</v>
@@ -2171,49 +2171,49 @@
         <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>2.76</v>
       </c>
       <c r="U11" t="n">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.83</v>
+        <v>3.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
         <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.9</v>
+        <v>2.57</v>
       </c>
       <c r="P12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R12" t="n">
         <v>1.77</v>
       </c>
       <c r="S12" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="AB12" t="n">
         <v>1.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.15</v>
+        <v>4.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
         <v>1.03</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>3.13</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>3.99</v>
+        <v>3.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="P14" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -1341,13 +1341,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '12', '23', '28']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46188.58333333334</v>
@@ -1497,26 +1497,26 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '73']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1599,28 +1599,28 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46188.58680555555</v>
@@ -1656,26 +1656,26 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '17', '84']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '34', '42', '63']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
@@ -1758,28 +1758,28 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46188.625</v>
@@ -1841,25 +1841,25 @@
         <v>1.58</v>
       </c>
       <c r="O9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P9" t="n">
         <v>4.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
         <v>2.3</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T9" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
         <v>1.5</v>
@@ -1877,22 +1877,22 @@
         <v>4.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
         <v>2.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD9" t="n">
         <v>1.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG9" t="n">
         <v>1.95</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="S11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.42</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.33</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
         <v>3.21</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2318,13 +2318,13 @@
         <v>2.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
         <v>3.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="R12" t="n">
         <v>1.77</v>
@@ -2333,13 +2333,13 @@
         <v>1.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="U12" t="n">
         <v>3.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="W12" t="n">
         <v>1.03</v>
@@ -2351,16 +2351,16 @@
         <v>1.56</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD12" t="n">
         <v>1.11</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK12" t="n">
         <v>1.65</v>
@@ -2513,7 +2513,7 @@
         <v>2.59</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AB13" t="n">
         <v>1.57</v>
@@ -2633,16 +2633,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="O14" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="P14" t="n">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="R14" t="n">
         <v>1.9</v>
@@ -2654,31 +2654,31 @@
         <v>2.41</v>
       </c>
       <c r="U14" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AA14" t="n">
         <v>2.29</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AD14" t="n">
         <v>1.16</v>
@@ -2687,10 +2687,10 @@
         <v>1.02</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-06-15.xlsx
+++ b/jogos_2026-06-15.xlsx
@@ -2477,22 +2477,22 @@
         <v>1.91</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3.18</v>
+        <v>3.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="R13" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="T13" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="U13" t="n">
         <v>3.28</v>
@@ -2501,37 +2501,37 @@
         <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AB13" t="n">
         <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O14" t="n">
         <v>2.98</v>
       </c>
       <c r="P14" t="n">
-        <v>2.71</v>
+        <v>2.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.12</v>
+        <v>3.31</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="S14" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="T14" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="U14" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1.16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
